--- a/stations/output/MAN_Interlocking_Program.xlsx
+++ b/stations/output/MAN_Interlocking_Program.xlsx
@@ -20236,12 +20236,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>M0</t>
+          <t>M22(VI)</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -20259,58 +20259,42 @@
           <t>Shunt</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>5II+</t>
-        </is>
-      </c>
+      <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="10" t="inlineStr"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19, 15, 13</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>13, 7</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="inlineStr">
+          <t>21, 7</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr"/>
+      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>5II</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
       <c r="O14" s="12" t="inlineStr">
         <is>
           <t>9II</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>5I</t>
-        </is>
-      </c>
+      <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr"/>
       <c r="S14" s="12" t="inlineStr"/>
       <c r="T14" s="11" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="U14" s="12" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="V14" s="11" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="U14" s="12" t="inlineStr"/>
+      <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
       <c r="X14" s="11" t="inlineStr"/>
       <c r="Y14" s="12" t="inlineStr"/>
@@ -20323,12 +20307,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>M0</t>
+          <t>M22(VII)</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -20348,52 +20332,48 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>5II-</t>
+          <t>5II+</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="10" t="inlineStr"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21, 19, 15, 13</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>13, 7</t>
-        </is>
-      </c>
-      <c r="L15" s="11" t="inlineStr"/>
-      <c r="M15" s="12" t="inlineStr">
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>5II</t>
         </is>
       </c>
+      <c r="M15" s="12" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr">
         <is>
           <t>9II</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>5I</t>
+        </is>
+      </c>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
       <c r="T15" s="11" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="U15" s="12" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="V15" s="11" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="U15" s="12" t="inlineStr"/>
+      <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
       <c r="X15" s="11" t="inlineStr"/>
       <c r="Y15" s="12" t="inlineStr"/>
@@ -20429,7 +20409,11 @@
           <t>Shunt</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>5II+</t>
+        </is>
+      </c>
       <c r="H16" s="9" t="inlineStr"/>
       <c r="I16" s="10" t="inlineStr"/>
       <c r="J16" s="11" t="inlineStr">
@@ -20442,19 +20426,23 @@
           <t>21, 7</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr"/>
-      <c r="M16" s="12" t="inlineStr">
+      <c r="L16" s="11" t="inlineStr">
         <is>
           <t>5II</t>
         </is>
       </c>
+      <c r="M16" s="12" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr"/>
       <c r="O16" s="12" t="inlineStr">
         <is>
           <t>9II</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr"/>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>5I</t>
+        </is>
+      </c>
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr"/>
@@ -20502,7 +20490,7 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>5II+</t>
+          <t>5II-</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr"/>
@@ -20517,23 +20505,19 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L17" s="11" t="inlineStr">
+      <c r="L17" s="11" t="inlineStr"/>
+      <c r="M17" s="12" t="inlineStr">
         <is>
           <t>5II</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr">
         <is>
           <t>9II</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>5I</t>
-        </is>
-      </c>
+      <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
@@ -20556,12 +20540,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>M22(VI)</t>
+          <t>M28(R2)</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -20579,50 +20563,46 @@
           <t>Shunt</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>5II+</t>
-        </is>
-      </c>
+      <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="9" t="inlineStr"/>
       <c r="I18" s="10" t="inlineStr"/>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>19, 15, 13</t>
-        </is>
-      </c>
+      <c r="J18" s="11" t="inlineStr"/>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>21, 7</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
+          <t>23, 13, 7</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr"/>
+      <c r="M18" s="12" t="inlineStr">
         <is>
           <t>5II</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr"/>
       <c r="O18" s="12" t="inlineStr">
         <is>
           <t>9II</t>
         </is>
       </c>
-      <c r="P18" s="11" t="inlineStr">
-        <is>
-          <t>5I</t>
-        </is>
-      </c>
+      <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr"/>
       <c r="S18" s="12" t="inlineStr"/>
       <c r="T18" s="11" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="U18" s="12" t="inlineStr"/>
-      <c r="V18" s="11" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U18" s="12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V18" s="11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="W18" s="12" t="inlineStr"/>
       <c r="X18" s="11" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
@@ -20635,12 +20615,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>M22(VII)</t>
+          <t>M28(R1)</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -20660,44 +20640,56 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>5II-</t>
+          <t>5II+</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr"/>
       <c r="I19" s="10" t="inlineStr"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>21, 19, 15, 13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr"/>
-      <c r="M19" s="12" t="inlineStr">
+          <t>13, 7</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
         <is>
           <t>5II</t>
         </is>
       </c>
+      <c r="M19" s="12" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr">
         <is>
           <t>9II</t>
         </is>
       </c>
-      <c r="P19" s="11" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>5I</t>
+        </is>
+      </c>
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
       <c r="T19" s="11" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="U19" s="12" t="inlineStr"/>
-      <c r="V19" s="11" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U19" s="12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="W19" s="12" t="inlineStr"/>
       <c r="X19" s="11" t="inlineStr"/>
       <c r="Y19" s="12" t="inlineStr"/>
@@ -20710,12 +20702,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>M28</t>
+          <t>M28(R2)</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -20793,12 +20785,12 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>M28</t>
+          <t>M28(R1)</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -20823,10 +20815,14 @@
       </c>
       <c r="H21" s="9" t="inlineStr"/>
       <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>23, 13, 7</t>
+          <t>13, 7</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr"/>
@@ -28400,8 +28396,14 @@
       <c r="B3" s="12" t="n">
         <v>190</v>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="12" t="n"/>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>165</v>
+      </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
           <t>S3/M3</t>
@@ -28420,8 +28422,14 @@
       <c r="B4" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="12" t="n"/>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>S20/M20</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>180</v>
+      </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
           <t>S9/M9</t>
@@ -28440,15 +28448,21 @@
       <c r="B5" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>S18/M18</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>195</v>
+      </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
           <t>S15/M15</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6">
@@ -28460,15 +28474,21 @@
       <c r="B6" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="12" t="n"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>S3/M3</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>150</v>
+      </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
           <t>CON</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>75</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7">
@@ -28480,15 +28500,21 @@
       <c r="B7" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="12" t="n"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>S16/M16</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>255</v>
+      </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
           <t>S18/M18</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>180</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8">
@@ -28500,8 +28526,14 @@
       <c r="B8" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="12" t="n"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>S12/M12</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>255</v>
+      </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
           <t>S20/M20</t>
@@ -28520,15 +28552,21 @@
       <c r="B9" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="12" t="n"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>S14/M14</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>255</v>
+      </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
           <t>NEL</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -28540,15 +28578,21 @@
       <c r="B10" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="12" t="n"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>S5/M5</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>230</v>
+      </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
           <t>S4/M4</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -28560,15 +28604,21 @@
       <c r="B11" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="12" t="n"/>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>S4/M4</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>240</v>
+      </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
           <t>S16/M16</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>80</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12">
@@ -28580,8 +28630,14 @@
       <c r="B12" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="12" t="n"/>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>S7/M7</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>230</v>
+      </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
           <t>S5/M5</t>
@@ -28600,15 +28656,21 @@
       <c r="B13" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="12" t="n"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>S6/M6</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>240</v>
+      </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
           <t>S11/M11</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>90</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14">
@@ -28620,8 +28682,14 @@
       <c r="B14" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="12" t="n"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>S9/M9</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>230</v>
+      </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
           <t>S7/M7</t>
@@ -28640,15 +28708,21 @@
       <c r="B15" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="12" t="n"/>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>S8/M8</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>245</v>
+      </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
           <t>S13/M13</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>85</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16">
@@ -28660,71 +28734,101 @@
       <c r="B16" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="12" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>S10/M10</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>245</v>
+      </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
           <t>S21/M21</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="32" t="n"/>
       <c r="B17" s="12" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="12" t="n"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>S11/M11</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>155</v>
+      </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
           <t>S6/M6</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="32" t="n"/>
       <c r="B18" s="12" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="12" t="n"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>S13/M13</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>255</v>
+      </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
           <t>S17/M17</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="32" t="n"/>
       <c r="B19" s="12" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="12" t="n"/>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>S15/M15</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>255</v>
+      </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
           <t>S19/M19</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>185</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="32" t="n"/>
       <c r="B20" s="12" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="12" t="n"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>170</v>
+      </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
           <t>S14/M14</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>170</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21">
@@ -28738,7 +28842,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>80</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22">
@@ -28766,7 +28870,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24">
@@ -28780,7 +28884,7 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25">
@@ -28794,7 +28898,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26">
@@ -28808,7 +28912,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27">
@@ -28822,7 +28926,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28">
@@ -28836,7 +28940,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>65</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29">
@@ -28864,7 +28968,7 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>90</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31">
@@ -29090,7 +29194,7 @@
       </c>
       <c r="C1" s="36" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Operational Parameters</t>
         </is>
       </c>
       <c r="D1" s="37" t="inlineStr">
@@ -30200,7 +30304,7 @@
       </c>
       <c r="B65" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S1 125650
+          <t xml:space="preserve">    S1 125650 123979 350
 </t>
         </is>
       </c>
@@ -30228,7 +30332,7 @@
       </c>
       <c r="B67" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S20/M20 125955
+          <t xml:space="preserve">    S20/M20 125955 127848 350
 </t>
         </is>
       </c>
@@ -30242,7 +30346,7 @@
       </c>
       <c r="B68" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S3/M3 127148
+          <t xml:space="preserve">    S3/M3 127148 125650 350
 </t>
         </is>
       </c>
@@ -30256,7 +30360,7 @@
       </c>
       <c r="B69" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S18/M18 127159
+          <t xml:space="preserve">    S18/M18 127159 129202 350
 </t>
         </is>
       </c>
@@ -30284,7 +30388,7 @@
       </c>
       <c r="B71" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S16/M16 127848
+          <t xml:space="preserve">    S16/M16 127848 130963 350
 </t>
         </is>
       </c>
@@ -30298,7 +30402,7 @@
       </c>
       <c r="B72" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S12/M12 127945
+          <t xml:space="preserve">    S12/M12 127945 130963 350
 </t>
         </is>
       </c>
@@ -30312,7 +30416,7 @@
       </c>
       <c r="B73" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S14/M14 127951
+          <t xml:space="preserve">    S14/M14 127951 130963 350
 </t>
         </is>
       </c>
@@ -30326,7 +30430,7 @@
       </c>
       <c r="B74" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S5/M5 128141
+          <t xml:space="preserve">    S5/M5 128141 125650 350
 </t>
         </is>
       </c>
@@ -30340,7 +30444,7 @@
       </c>
       <c r="B75" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S7/M7 128144
+          <t xml:space="preserve">    S7/M7 128144 125650 350
 </t>
         </is>
       </c>
@@ -30354,7 +30458,7 @@
       </c>
       <c r="B76" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S9/M9 128137
+          <t xml:space="preserve">    S9/M9 128137 125650 350
 </t>
         </is>
       </c>
@@ -30382,7 +30486,7 @@
       </c>
       <c r="B78" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S4/M4 128361
+          <t xml:space="preserve">    S4/M4 128361 130963 350
 </t>
         </is>
       </c>
@@ -30396,7 +30500,7 @@
       </c>
       <c r="B79" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S6/M6 128361
+          <t xml:space="preserve">    S6/M6 128361 130963 350
 </t>
         </is>
       </c>
@@ -30410,7 +30514,7 @@
       </c>
       <c r="B80" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S8/M8 128295
+          <t xml:space="preserve">    S8/M8 128295 130963 350
 </t>
         </is>
       </c>
@@ -30438,7 +30542,7 @@
       </c>
       <c r="B82" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S10/M10 128302
+          <t xml:space="preserve">    S10/M10 128302 130963 350
 </t>
         </is>
       </c>
@@ -30480,7 +30584,7 @@
       </c>
       <c r="B85" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S15/M15 128571
+          <t xml:space="preserve">    S15/M15 128571 125650 350
 </t>
         </is>
       </c>
@@ -30536,7 +30640,7 @@
       </c>
       <c r="B89" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S13/M13 128673
+          <t xml:space="preserve">    S13/M13 128673 125650 350
 </t>
         </is>
       </c>
@@ -30550,7 +30654,7 @@
       </c>
       <c r="B90" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S11/M11 128703
+          <t xml:space="preserve">    S11/M11 128703 127148 350
 </t>
         </is>
       </c>
@@ -30592,7 +30696,7 @@
       </c>
       <c r="B93" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S2 129202
+          <t xml:space="preserve">    S2 129202 130963 350
 </t>
         </is>
       </c>
@@ -30604,12 +30708,7 @@
 </t>
         </is>
       </c>
-      <c r="B94" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    M0 128271
-</t>
-        </is>
-      </c>
+      <c r="B94" s="38" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="38" t="inlineStr">
@@ -30893,7 +30992,7 @@
     <row r="126">
       <c r="A126" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SIG M0
+          <t xml:space="preserve">        SIG M28
 </t>
         </is>
       </c>

--- a/stations/output/MAN_Interlocking_Program.xlsx
+++ b/stations/output/MAN_Interlocking_Program.xlsx
@@ -462,15 +462,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -479,37 +470,6 @@
         <color theme="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -531,30 +491,6 @@
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
@@ -585,6 +521,39 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -592,6 +561,15 @@
       <top style="medium">
         <color theme="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -609,6 +587,17 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color theme="1"/>
@@ -639,12 +628,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -788,9 +788,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -818,29 +815,42 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1183,49 +1193,49 @@
       <c r="B1" s="21" t="n"/>
       <c r="C1" s="21" t="n"/>
       <c r="D1" s="21" t="n"/>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>ZIRCON</t>
         </is>
       </c>
-      <c r="F1" s="60" t="n"/>
+      <c r="F1" s="62" t="n"/>
     </row>
     <row r="2" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A2" s="22" t="n"/>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="61" t="n"/>
-      <c r="F2" s="62" t="n"/>
+      <c r="A2" s="58" t="n"/>
+      <c r="B2" s="59" t="n"/>
+      <c r="C2" s="59" t="n"/>
+      <c r="D2" s="59" t="n"/>
+      <c r="E2" s="63" t="n"/>
+      <c r="F2" s="64" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="49" t="n"/>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
-      <c r="E3" s="49" t="n"/>
+      <c r="A3" s="58" t="n"/>
+      <c r="B3" s="59" t="n"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="59" t="n"/>
+      <c r="E3" s="59" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.1</t>
+          <t>v1.0.2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="49" t="n"/>
-      <c r="C4" s="49" t="n"/>
-      <c r="D4" s="49" t="n"/>
-      <c r="E4" s="49" t="n"/>
-      <c r="F4" s="23" t="n"/>
+      <c r="A4" s="58" t="n"/>
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="60" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n"/>
+      <c r="A5" s="58" t="n"/>
       <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Interlocking Program</t>
         </is>
       </c>
-      <c r="F5" s="23" t="n"/>
+      <c r="F5" s="60" t="n"/>
     </row>
     <row r="6" ht="14.4" customHeight="1">
       <c r="A6" s="24" t="n"/>
@@ -1240,94 +1250,92 @@
       <c r="F7" s="25" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="49" t="inlineStr">
-        <is>
-          <t>Mangualde (MAN)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="n"/>
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>Mangualde (NOT REAL DATA - FOR TESTING ONLY) (MAN)</t>
+        </is>
+      </c>
+      <c r="F8" s="66" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>Linha da Beira Alta</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n"/>
+      <c r="F9" s="66" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="49" t="n"/>
-      <c r="F10" s="23" t="n"/>
+      <c r="A10" s="58" t="n"/>
+      <c r="B10" s="59" t="n"/>
+      <c r="C10" s="59" t="n"/>
+      <c r="D10" s="59" t="n"/>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="60" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="49" t="n"/>
-      <c r="C11" s="49" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="23" t="n"/>
+      <c r="A11" s="58" t="n"/>
+      <c r="B11" s="59" t="n"/>
+      <c r="C11" s="59" t="n"/>
+      <c r="D11" s="59" t="n"/>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="60" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="49" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="A12" s="58" t="n"/>
+      <c r="B12" s="59" t="n"/>
+      <c r="C12" s="59" t="n"/>
+      <c r="D12" s="59" t="n"/>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="60" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="49" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="A13" s="58" t="n"/>
+      <c r="B13" s="59" t="n"/>
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="59" t="n"/>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="60" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="23" t="n"/>
+      <c r="A14" s="58" t="n"/>
+      <c r="B14" s="59" t="n"/>
+      <c r="C14" s="59" t="n"/>
+      <c r="D14" s="59" t="n"/>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="60" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="49" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
-      <c r="F15" s="23" t="n"/>
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="59" t="n"/>
+      <c r="C15" s="59" t="n"/>
+      <c r="D15" s="59" t="n"/>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="60" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="49" t="n"/>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="23" t="n"/>
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="59" t="n"/>
+      <c r="C16" s="59" t="n"/>
+      <c r="D16" s="59" t="n"/>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="60" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="49" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="49" t="n"/>
-      <c r="E17" s="49" t="n"/>
-      <c r="F17" s="23" t="n"/>
+      <c r="A17" s="58" t="n"/>
+      <c r="B17" s="59" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="59" t="n"/>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="60" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="23" t="n"/>
+      <c r="A18" s="58" t="n"/>
+      <c r="B18" s="59" t="n"/>
+      <c r="C18" s="59" t="n"/>
+      <c r="D18" s="59" t="n"/>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="60" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
@@ -1335,11 +1343,11 @@
           <t>Diogo Luís</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="23" t="n"/>
+      <c r="B19" s="59" t="n"/>
+      <c r="C19" s="59" t="n"/>
+      <c r="D19" s="59" t="n"/>
+      <c r="E19" s="59" t="n"/>
+      <c r="F19" s="60" t="n"/>
     </row>
     <row r="20" ht="16.2" customHeight="1" thickBot="1">
       <c r="A20" s="31" t="inlineStr">
@@ -1355,9 +1363,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="B5:E6"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="E1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1385,310 +1393,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -1753,7 +1761,7 @@
       </c>
       <c r="S6" s="12" t="inlineStr">
         <is>
-          <t>2, D2</t>
+          <t>2, B2</t>
         </is>
       </c>
       <c r="T6" s="11" t="inlineStr"/>
@@ -2243,7 +2251,7 @@
       </c>
       <c r="S12" s="12" t="inlineStr">
         <is>
-          <t>4, 2, D2</t>
+          <t>4, 2, B2</t>
         </is>
       </c>
       <c r="T12" s="11" t="inlineStr">
@@ -2405,7 +2413,7 @@
       </c>
       <c r="S14" s="12" t="inlineStr">
         <is>
-          <t>4, 2, D2</t>
+          <t>4, 2, B2</t>
         </is>
       </c>
       <c r="T14" s="11" t="inlineStr"/>
@@ -2498,12 +2506,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S230/M230</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>NEL</t>
+          <t>SIAF</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -2524,25 +2532,21 @@
       <c r="G16" s="10" t="inlineStr"/>
       <c r="H16" s="9" t="inlineStr"/>
       <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>1II</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="inlineStr"/>
+      <c r="J16" s="11" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>1I, 1II</t>
+        </is>
+      </c>
       <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="N16" s="11" t="inlineStr"/>
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>A1, 1II, A2, A3</t>
+          <t>1I, 1II, A2, A3</t>
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr">
@@ -2551,7 +2555,11 @@
         </is>
       </c>
       <c r="T16" s="11" t="inlineStr"/>
-      <c r="U16" s="12" t="inlineStr"/>
+      <c r="U16" s="12" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
       <c r="X16" s="11" t="inlineStr"/>
@@ -2565,12 +2573,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S230/M230</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>NEL</t>
+          <t>SIAF</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -2591,26 +2599,26 @@
       <c r="G17" s="10" t="inlineStr"/>
       <c r="H17" s="9" t="inlineStr"/>
       <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>1II</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr"/>
+      <c r="J17" s="11" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>1I, 1II</t>
+        </is>
+      </c>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="N17" s="11" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
       <c r="T17" s="11" t="inlineStr"/>
-      <c r="U17" s="12" t="inlineStr"/>
+      <c r="U17" s="12" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="12" t="inlineStr"/>
       <c r="X17" s="11" t="inlineStr"/>
@@ -2624,12 +2632,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>S23/M23</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>SIAF</t>
+          <t>NEL</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -2650,21 +2658,25 @@
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="9" t="inlineStr"/>
       <c r="I18" s="10" t="inlineStr"/>
-      <c r="J18" s="11" t="inlineStr"/>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>1I, 1II</t>
-        </is>
-      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr"/>
       <c r="L18" s="11" t="inlineStr"/>
       <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O18" s="12" t="inlineStr"/>
       <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>1I, 1II, A2, A3</t>
+          <t>A1, 1II, A2, A3</t>
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr">
@@ -2673,11 +2685,7 @@
         </is>
       </c>
       <c r="T18" s="11" t="inlineStr"/>
-      <c r="U18" s="12" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr"/>
       <c r="X18" s="11" t="inlineStr"/>
@@ -2691,12 +2699,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>S23/M23</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>SIAF</t>
+          <t>NEL</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -2717,26 +2725,26 @@
       <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="9" t="inlineStr"/>
       <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="11" t="inlineStr"/>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>1I, 1II</t>
-        </is>
-      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr"/>
       <c r="L19" s="11" t="inlineStr"/>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O19" s="12" t="inlineStr"/>
       <c r="P19" s="11" t="inlineStr"/>
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
       <c r="T19" s="11" t="inlineStr"/>
-      <c r="U19" s="12" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="U19" s="12" t="inlineStr"/>
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="12" t="inlineStr"/>
       <c r="X19" s="11" t="inlineStr"/>
@@ -4872,7 +4880,7 @@
       </c>
       <c r="R46" s="11" t="inlineStr">
         <is>
-          <t>D1, D2, 2, 4, 6/8, 10, IV</t>
+          <t>B1, B2, 2, 4, 6/8, 10, IV</t>
         </is>
       </c>
       <c r="S46" s="12" t="inlineStr">
@@ -5926,7 +5934,7 @@
       <c r="Q60" s="12" t="inlineStr"/>
       <c r="R60" s="11" t="inlineStr">
         <is>
-          <t>D1, D2, 2, 4, 6/8, 19, 15, 13, 7, IIIA</t>
+          <t>B1, B2, 2, 4, 6/8, 19, 15, 13, 7, IIIA</t>
         </is>
       </c>
       <c r="S60" s="12" t="inlineStr">
@@ -6021,7 +6029,7 @@
       <c r="Q61" s="12" t="inlineStr"/>
       <c r="R61" s="11" t="inlineStr">
         <is>
-          <t>D1, D2, 2, 4, 6/8, 19, 15, 13, 7, IIIA</t>
+          <t>B1, B2, 2, 4, 6/8, 19, 15, 13, 7, IIIA</t>
         </is>
       </c>
       <c r="S61" s="12" t="inlineStr">
@@ -6120,7 +6128,7 @@
       <c r="Q62" s="12" t="inlineStr"/>
       <c r="R62" s="11" t="inlineStr">
         <is>
-          <t>D1, D2, 2, 4, 6/8, 21, 19, 15, 13, 7, IIIA</t>
+          <t>B1, B2, 2, 4, 6/8, 21, 19, 15, 13, 7, IIIA</t>
         </is>
       </c>
       <c r="S62" s="12" t="inlineStr">
@@ -6215,7 +6223,7 @@
       <c r="Q63" s="12" t="inlineStr"/>
       <c r="R63" s="11" t="inlineStr">
         <is>
-          <t>D1, D2, 2, 4, 6/8, 21, 19, 15, 13, 7, IIIA</t>
+          <t>B1, B2, 2, 4, 6/8, 21, 19, 15, 13, 7, IIIA</t>
         </is>
       </c>
       <c r="S63" s="12" t="inlineStr">
@@ -6958,7 +6966,7 @@
       <c r="Q72" s="12" t="inlineStr"/>
       <c r="R72" s="11" t="inlineStr">
         <is>
-          <t>D1, D2, 2, I</t>
+          <t>B1, B2, 2, I</t>
         </is>
       </c>
       <c r="S72" s="12" t="inlineStr">
@@ -7428,7 +7436,7 @@
       <c r="Q78" s="12" t="inlineStr"/>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>D1, D2, 2, 4, II</t>
+          <t>B1, B2, 2, 4, II</t>
         </is>
       </c>
       <c r="S78" s="12" t="inlineStr">
@@ -7519,7 +7527,7 @@
       </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
-          <t>D1, D2, 2, 4, II</t>
+          <t>B1, B2, 2, 4, II</t>
         </is>
       </c>
       <c r="S79" s="12" t="inlineStr">
@@ -8071,7 +8079,7 @@
       <c r="Q87" s="12" t="inlineStr"/>
       <c r="R87" s="11" t="inlineStr">
         <is>
-          <t>D1, D2, 2, 4, 6/8, 10, III</t>
+          <t>B1, B2, 2, 4, 6/8, 10, III</t>
         </is>
       </c>
       <c r="S87" s="12" t="inlineStr">
@@ -8158,7 +8166,7 @@
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>D1, D2, 2, 4, 6/8, 10, III</t>
+          <t>B1, B2, 2, 4, 6/8, 10, III</t>
         </is>
       </c>
       <c r="S88" s="12" t="inlineStr">
@@ -8809,310 +8817,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -9389,7 +9397,7 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>2, D2, D1</t>
+          <t>2, B2, B1</t>
         </is>
       </c>
       <c r="S9" s="12" t="inlineStr"/>
@@ -9539,7 +9547,7 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>6/8, 4, 2, D2, D1</t>
+          <t>6/8, 4, 2, B2, B1</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr"/>
@@ -9677,7 +9685,7 @@
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr">
         <is>
-          <t>4, 2, D2, D1</t>
+          <t>4, 2, B2, B1</t>
         </is>
       </c>
       <c r="S13" s="12" t="inlineStr"/>
@@ -9827,7 +9835,7 @@
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>10, 6/8, 4, 2, D2, D1</t>
+          <t>10, 6/8, 4, 2, B2, B1</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr"/>
@@ -9965,7 +9973,7 @@
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>10, 6/8, 4, 2, D2, D1</t>
+          <t>10, 6/8, 4, 2, B2, B1</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr"/>
@@ -10103,7 +10111,7 @@
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>6/8, 4, 2, D2, D1</t>
+          <t>6/8, 4, 2, B2, B1</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr"/>
@@ -12853,310 +12861,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -16111,310 +16119,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -19369,310 +19377,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -20047,7 +20055,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>S23/M23</t>
+          <t>S230/M230</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -20873,7 +20881,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -21131,7 +21139,7 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
@@ -21198,7 +21206,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
@@ -21261,7 +21269,7 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
@@ -21328,7 +21336,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -21391,7 +21399,7 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -21454,7 +21462,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
@@ -21511,7 +21519,7 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -23729,310 +23737,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -24964,7 +24972,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -25800,7 +25808,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -26048,7 +26056,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -26123,7 +26131,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -26324,7 +26332,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -28336,24 +28344,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="B1" s="66" t="n"/>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="B1" s="70" t="n"/>
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Approach Route Cancel</t>
         </is>
       </c>
-      <c r="D1" s="66" t="n"/>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="D1" s="70" t="n"/>
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Emergency Route Cancel</t>
         </is>
       </c>
-      <c r="F1" s="66" t="n"/>
+      <c r="F1" s="70" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -28361,27 +28369,27 @@
           <t>Track</t>
         </is>
       </c>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="C2" s="50" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D2" s="50" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="E2" s="50" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="F2" s="57" t="inlineStr">
+      <c r="F2" s="56" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
@@ -28728,7 +28736,7 @@
     <row r="16">
       <c r="A16" s="32" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
@@ -29224,7 +29232,7 @@
       </c>
       <c r="D2" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">station_name Mangualde
+          <t xml:space="preserve">station_name Mangualde (NOT REAL DATA - FOR TESTING ONLY)
 </t>
         </is>
       </c>
@@ -29238,7 +29246,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A1 125838 125657
+          <t xml:space="preserve">    A1 25838 25657
 </t>
         </is>
       </c>
@@ -29264,7 +29272,7 @@
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1II 125950 125838 125892
+          <t xml:space="preserve">    1II 25950 25838 25892
 </t>
         </is>
       </c>
@@ -29290,7 +29298,7 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1I 125847 125892 125757
+          <t xml:space="preserve">    1I 25847 25892 25757
 </t>
         </is>
       </c>
@@ -29316,7 +29324,7 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A2 126201 125950
+          <t xml:space="preserve">    A2 26201 25950
 </t>
         </is>
       </c>
@@ -29342,7 +29350,7 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A3 127153 126201
+          <t xml:space="preserve">    A3 27153 26201
 </t>
         </is>
       </c>
@@ -29363,7 +29371,7 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A4 127458 127153
+          <t xml:space="preserve">    A4 27458 27153
 </t>
         </is>
       </c>
@@ -29384,7 +29392,7 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A5 127726 127458
+          <t xml:space="preserve">    A5 27726 27458
 </t>
         </is>
       </c>
@@ -29405,7 +29413,7 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3 127843 127789 127726
+          <t xml:space="preserve">    3 27843 27789 27726
 </t>
         </is>
       </c>
@@ -29426,7 +29434,7 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5I 127940 127917 127789
+          <t xml:space="preserve">    5I 27940 27917 27789
 </t>
         </is>
       </c>
@@ -29447,7 +29455,7 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5II 127946 127792 127917
+          <t xml:space="preserve">    5II 27946 27792 27917
 </t>
         </is>
       </c>
@@ -29468,7 +29476,7 @@
       </c>
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    IA 128146 127843
+          <t xml:space="preserve">    IA 28146 27843
 </t>
         </is>
       </c>
@@ -29489,7 +29497,7 @@
       </c>
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    IIA 128149 127940
+          <t xml:space="preserve">    IIA 28149 27940
 </t>
         </is>
       </c>
@@ -29510,7 +29518,7 @@
       </c>
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    IIIA 128142 127946
+          <t xml:space="preserve">    IIIA 28142 27946
 </t>
         </is>
       </c>
@@ -29531,7 +29539,7 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    11I 128230 128257 128146
+          <t xml:space="preserve">    11I 28230 28257 28146
 </t>
         </is>
       </c>
@@ -29552,7 +29560,7 @@
       </c>
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    17 128296 128356 128230
+          <t xml:space="preserve">    17 28296 28356 28230
 </t>
         </is>
       </c>
@@ -29572,7 +29580,7 @@
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    9I 128225 128221 128149
+          <t xml:space="preserve">    9I 28225 28221 28149
 </t>
         </is>
       </c>
@@ -29586,13 +29594,13 @@
     <row r="19">
       <c r="A19" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SWP S23/M23
+          <t xml:space="preserve">        SWP S230/M230
 </t>
         </is>
       </c>
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    11II 128356 128225 128257
+          <t xml:space="preserve">    11II 28356 28225 28257
 </t>
         </is>
       </c>
@@ -29612,7 +29620,7 @@
       </c>
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    7 128218 128189 128142
+          <t xml:space="preserve">    7 28218 28189 28142
 </t>
         </is>
       </c>
@@ -29632,7 +29640,7 @@
       </c>
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    9II 128290 128218 128221
+          <t xml:space="preserve">    9II 28290 28218 28221
 </t>
         </is>
       </c>
@@ -29652,7 +29660,7 @@
       </c>
       <c r="B22" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    13 128225 128211 128189
+          <t xml:space="preserve">    13 28225 28211 28189
 </t>
         </is>
       </c>
@@ -29672,7 +29680,7 @@
       </c>
       <c r="B23" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    15 128297 128265 128225
+          <t xml:space="preserve">    15 28297 28265 28225
 </t>
         </is>
       </c>
@@ -29692,7 +29700,7 @@
       </c>
       <c r="B24" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    19 128325 128297 128265
+          <t xml:space="preserve">    19 28325 28297 28265
 </t>
         </is>
       </c>
@@ -29712,7 +29720,7 @@
       </c>
       <c r="B25" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    21 128355 128355 128297
+          <t xml:space="preserve">    21 28355 28355 28297
 </t>
         </is>
       </c>
@@ -29732,7 +29740,7 @@
       </c>
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    23 128269 128261 128211
+          <t xml:space="preserve">    23 28269 28261 28211
 </t>
         </is>
       </c>
@@ -29752,7 +29760,7 @@
       </c>
       <c r="B27" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    I 128708 128356
+          <t xml:space="preserve">    I 28708 28356
 </t>
         </is>
       </c>
@@ -29772,7 +29780,7 @@
       </c>
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    II 128678 128356
+          <t xml:space="preserve">    II 28678 28356
 </t>
         </is>
       </c>
@@ -29792,7 +29800,7 @@
       </c>
       <c r="B29" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    III 128576 128290
+          <t xml:space="preserve">    III 28576 28290
 </t>
         </is>
       </c>
@@ -29812,7 +29820,7 @@
       </c>
       <c r="B30" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    IV 128576 128297
+          <t xml:space="preserve">    IV 28576 28297
 </t>
         </is>
       </c>
@@ -29827,7 +29835,7 @@
       </c>
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    V 128607 128325
+          <t xml:space="preserve">    V 28607 28325
 </t>
         </is>
       </c>
@@ -29842,7 +29850,7 @@
       </c>
       <c r="B32" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    VI 128617 128355
+          <t xml:space="preserve">    VI 28617 28355
 </t>
         </is>
       </c>
@@ -29856,7 +29864,7 @@
       </c>
       <c r="B33" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2 128809 128751 128708
+          <t xml:space="preserve">    2 28809 28751 28708
 </t>
         </is>
       </c>
@@ -29870,7 +29878,7 @@
       </c>
       <c r="B34" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4 128751 128700 128678
+          <t xml:space="preserve">    4 28751 28700 28678
 </t>
         </is>
       </c>
@@ -29884,7 +29892,7 @@
       </c>
       <c r="B35" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6/8 128700 128617 128607 128640
+          <t xml:space="preserve">    6/8 28700 28617 28607 28640
 </t>
         </is>
       </c>
@@ -29898,7 +29906,7 @@
       </c>
       <c r="B36" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    10 128640 128576 128576
+          <t xml:space="preserve">    10 28640 28576 28576
 </t>
         </is>
       </c>
@@ -29912,7 +29920,7 @@
       </c>
       <c r="B37" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    D2 129089 128809
+          <t xml:space="preserve">    B2 29089 28809
 </t>
         </is>
       </c>
@@ -29926,7 +29934,7 @@
       </c>
       <c r="B38" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    D1 129194 129089
+          <t xml:space="preserve">    B1 29194 29089
 </t>
         </is>
       </c>
@@ -29954,7 +29962,7 @@
       </c>
       <c r="B40" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1I 125762 125822
+          <t xml:space="preserve">    1I 25762 25822
 </t>
         </is>
       </c>
@@ -29968,7 +29976,7 @@
       </c>
       <c r="B41" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1II 125907 125863
+          <t xml:space="preserve">    1II 25907 25863
 </t>
         </is>
       </c>
@@ -29982,7 +29990,7 @@
       </c>
       <c r="B42" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3 127746 127823
+          <t xml:space="preserve">    3 27746 27823
 </t>
         </is>
       </c>
@@ -29996,7 +30004,7 @@
       </c>
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5I 127815 127893
+          <t xml:space="preserve">    5I 27815 27893
 </t>
         </is>
       </c>
@@ -30010,7 +30018,7 @@
       </c>
       <c r="B44" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5II 127928 127873
+          <t xml:space="preserve">    5II 27928 27873
 </t>
         </is>
       </c>
@@ -30024,7 +30032,7 @@
       </c>
       <c r="B45" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    7 128165 128224
+          <t xml:space="preserve">    7 28165 28224
 </t>
         </is>
       </c>
@@ -30038,7 +30046,7 @@
       </c>
       <c r="B46" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    9I 128180 128222
+          <t xml:space="preserve">    9I 28180 28222
 </t>
         </is>
       </c>
@@ -30052,7 +30060,7 @@
       </c>
       <c r="B47" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    9II 128254 128197
+          <t xml:space="preserve">    9II 28254 28197
 </t>
         </is>
       </c>
@@ -30066,7 +30074,7 @@
       </c>
       <c r="B48" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    11I 128185 128240
+          <t xml:space="preserve">    11I 28185 28240
 </t>
         </is>
       </c>
@@ -30080,7 +30088,7 @@
       </c>
       <c r="B49" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    11II 128261 128207
+          <t xml:space="preserve">    11II 28261 28207
 </t>
         </is>
       </c>
@@ -30094,7 +30102,7 @@
       </c>
       <c r="B50" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    13 128200 128241
+          <t xml:space="preserve">    13 28200 28241
 </t>
         </is>
       </c>
@@ -30108,7 +30116,7 @@
       </c>
       <c r="B51" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    15 128229 128272
+          <t xml:space="preserve">    15 28229 28272
 </t>
         </is>
       </c>
@@ -30122,7 +30130,7 @@
       </c>
       <c r="B52" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    17 128250 128293
+          <t xml:space="preserve">    17 28250 28293
 </t>
         </is>
       </c>
@@ -30136,7 +30144,7 @@
       </c>
       <c r="B53" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    19 128268 128310
+          <t xml:space="preserve">    19 28268 28310
 </t>
         </is>
       </c>
@@ -30150,7 +30158,7 @@
       </c>
       <c r="B54" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    21 128301 128345
+          <t xml:space="preserve">    21 28301 28345
 </t>
         </is>
       </c>
@@ -30164,7 +30172,7 @@
       </c>
       <c r="B55" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    23 128238 128283
+          <t xml:space="preserve">    23 28238 28283
 </t>
         </is>
       </c>
@@ -30178,7 +30186,7 @@
       </c>
       <c r="B56" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2 128789 128724
+          <t xml:space="preserve">    2 28789 28724
 </t>
         </is>
       </c>
@@ -30192,7 +30200,7 @@
       </c>
       <c r="B57" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4 128727 128682
+          <t xml:space="preserve">    4 28727 28682
 </t>
         </is>
       </c>
@@ -30206,7 +30214,7 @@
       </c>
       <c r="B58" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6 128700 128648
+          <t xml:space="preserve">    6 28700 28648
 </t>
         </is>
       </c>
@@ -30220,7 +30228,7 @@
       </c>
       <c r="B59" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    8 128664 128616
+          <t xml:space="preserve">    8 28664 28616
 </t>
         </is>
       </c>
@@ -30234,7 +30242,7 @@
       </c>
       <c r="B60" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    10 128634 128583
+          <t xml:space="preserve">    10 28634 28583
 </t>
         </is>
       </c>
@@ -30248,7 +30256,7 @@
       </c>
       <c r="B61" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    C1 128295
+          <t xml:space="preserve">    C1 28295
 </t>
         </is>
       </c>
@@ -30262,7 +30270,7 @@
       </c>
       <c r="B62" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    C2 128606
+          <t xml:space="preserve">    C2 28606
 </t>
         </is>
       </c>
@@ -30276,7 +30284,7 @@
       </c>
       <c r="B63" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    C4 128616
+          <t xml:space="preserve">    C4 28616
 </t>
         </is>
       </c>
@@ -30304,7 +30312,7 @@
       </c>
       <c r="B65" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S1 125650 123979 350
+          <t xml:space="preserve">    S1 25650 23979 350
 </t>
         </is>
       </c>
@@ -30318,7 +30326,7 @@
       </c>
       <c r="B66" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S23/M23 125749
+          <t xml:space="preserve">    S230/M230 25749
 </t>
         </is>
       </c>
@@ -30332,7 +30340,7 @@
       </c>
       <c r="B67" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S20/M20 125955 127848 350
+          <t xml:space="preserve">    S20/M20 25955 27848 350
 </t>
         </is>
       </c>
@@ -30346,7 +30354,7 @@
       </c>
       <c r="B68" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S3/M3 127148 125650 350
+          <t xml:space="preserve">    S3/M3 27148 25650 350
 </t>
         </is>
       </c>
@@ -30360,7 +30368,7 @@
       </c>
       <c r="B69" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S18/M18 127159 129202 350
+          <t xml:space="preserve">    S18/M18 27159 29202 350
 </t>
         </is>
       </c>
@@ -30374,7 +30382,7 @@
       </c>
       <c r="B70" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M1 127725
+          <t xml:space="preserve">    M1 27725
 </t>
         </is>
       </c>
@@ -30388,7 +30396,7 @@
       </c>
       <c r="B71" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S16/M16 127848 130963 350
+          <t xml:space="preserve">    S16/M16 27848 30963 350
 </t>
         </is>
       </c>
@@ -30402,7 +30410,7 @@
       </c>
       <c r="B72" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S12/M12 127945 130963 350
+          <t xml:space="preserve">    S12/M12 27945 30963 350
 </t>
         </is>
       </c>
@@ -30416,7 +30424,7 @@
       </c>
       <c r="B73" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S14/M14 127951 130963 350
+          <t xml:space="preserve">    S14/M14 27951 30963 350
 </t>
         </is>
       </c>
@@ -30430,7 +30438,7 @@
       </c>
       <c r="B74" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S5/M5 128141 125650 350
+          <t xml:space="preserve">    S5/M5 28141 25650 350
 </t>
         </is>
       </c>
@@ -30444,7 +30452,7 @@
       </c>
       <c r="B75" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S7/M7 128144 125650 350
+          <t xml:space="preserve">    S7/M7 28144 25650 350
 </t>
         </is>
       </c>
@@ -30458,7 +30466,7 @@
       </c>
       <c r="B76" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S9/M9 128137 125650 350
+          <t xml:space="preserve">    S9/M9 28137 25650 350
 </t>
         </is>
       </c>
@@ -30472,7 +30480,7 @@
       </c>
       <c r="B77" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M26 128299
+          <t xml:space="preserve">    M26 28299
 </t>
         </is>
       </c>
@@ -30486,7 +30494,7 @@
       </c>
       <c r="B78" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S4/M4 128361 130963 350
+          <t xml:space="preserve">    S4/M4 28361 30963 350
 </t>
         </is>
       </c>
@@ -30500,7 +30508,7 @@
       </c>
       <c r="B79" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S6/M6 128361 130963 350
+          <t xml:space="preserve">    S6/M6 28361 30963 350
 </t>
         </is>
       </c>
@@ -30514,7 +30522,7 @@
       </c>
       <c r="B80" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S8/M8 128295 130963 350
+          <t xml:space="preserve">    S8/M8 28295 30963 350
 </t>
         </is>
       </c>
@@ -30528,7 +30536,7 @@
       </c>
       <c r="B81" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M28 128264
+          <t xml:space="preserve">    M28 28264
 </t>
         </is>
       </c>
@@ -30542,7 +30550,7 @@
       </c>
       <c r="B82" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S10/M10 128302 130963 350
+          <t xml:space="preserve">    S10/M10 28302 30963 350
 </t>
         </is>
       </c>
@@ -30556,7 +30564,7 @@
       </c>
       <c r="B83" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M24 128328
+          <t xml:space="preserve">    M24 28328
 </t>
         </is>
       </c>
@@ -30570,7 +30578,7 @@
       </c>
       <c r="B84" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M22 128358
+          <t xml:space="preserve">    M22 28358
 </t>
         </is>
       </c>
@@ -30584,7 +30592,7 @@
       </c>
       <c r="B85" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S15/M15 128571 125650 350
+          <t xml:space="preserve">    S15/M15 28571 25650 350
 </t>
         </is>
       </c>
@@ -30598,7 +30606,7 @@
       </c>
       <c r="B86" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S17/M17 128571
+          <t xml:space="preserve">    S17/M17 28571
 </t>
         </is>
       </c>
@@ -30612,7 +30620,7 @@
       </c>
       <c r="B87" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S19/M19 128599
+          <t xml:space="preserve">    S19/M19 28599
 </t>
         </is>
       </c>
@@ -30626,7 +30634,7 @@
       </c>
       <c r="B88" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S21/M21 128609
+          <t xml:space="preserve">    S21/M21 28609
 </t>
         </is>
       </c>
@@ -30640,7 +30648,7 @@
       </c>
       <c r="B89" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S13/M13 128673 125650 350
+          <t xml:space="preserve">    S13/M13 28673 25650 350
 </t>
         </is>
       </c>
@@ -30654,7 +30662,7 @@
       </c>
       <c r="B90" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S11/M11 128703 127148 350
+          <t xml:space="preserve">    S11/M11 28703 27148 350
 </t>
         </is>
       </c>
@@ -30668,7 +30676,7 @@
       </c>
       <c r="B91" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M2 128810
+          <t xml:space="preserve">    M2 28810
 </t>
         </is>
       </c>
@@ -30682,7 +30690,7 @@
       </c>
       <c r="B92" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M25 129088
+          <t xml:space="preserve">    M25 29088
 </t>
         </is>
       </c>
@@ -30696,7 +30704,7 @@
       </c>
       <c r="B93" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S2 129202 130963 350
+          <t xml:space="preserve">    S2 29202 30963 350
 </t>
         </is>
       </c>
@@ -31244,7 +31252,7 @@
     <row r="154">
       <c r="A154" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE A D2
+          <t xml:space="preserve">    NDE A B2
 </t>
         </is>
       </c>
@@ -31523,7 +31531,7 @@
     <row r="185">
       <c r="A185" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC D2
+          <t xml:space="preserve">SEC B2
 </t>
         </is>
       </c>
@@ -31532,7 +31540,7 @@
     <row r="186">
       <c r="A186" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE A D1
+          <t xml:space="preserve">    NDE A B1
 </t>
         </is>
       </c>
@@ -31550,7 +31558,7 @@
     <row r="188">
       <c r="A188" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC D1
+          <t xml:space="preserve">SEC B1
 </t>
         </is>
       </c>
@@ -31577,7 +31585,7 @@
     <row r="191">
       <c r="A191" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE B D2
+          <t xml:space="preserve">    NDE B B2
 </t>
         </is>
       </c>
